--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
+++ b/branches/master/StructureDefinition-hiv-arv-treatment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
